--- a/데이터/opened_course2024_2.xlsx
+++ b/데이터/opened_course2024_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d90a49386c3f612/바탕 화면/AI융개_팀플/데이터/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{FA6D6523-C504-477C-9A75-063CBFE23E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2FAED94-72CF-4D8A-9294-3A7ECBE1C6A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA18820-0AFE-4785-BBFF-FE29C56C4864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="공통교양2024_2" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -576,9 +575,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지능형IoT</t>
-  </si>
-  <si>
     <t>AI</t>
   </si>
   <si>
@@ -595,9 +591,6 @@
   </si>
   <si>
     <t>융합보안공학과</t>
-  </si>
-  <si>
-    <t>서비스·디자인공학과</t>
   </si>
   <si>
     <t>핵심전공</t>
@@ -957,6 +950,14 @@
   </si>
   <si>
     <t>서비스플랫폼디자인</t>
+  </si>
+  <si>
+    <t>지능형IoT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서비스디자인공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1366,16 +1367,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" t="s">
         <v>243</v>
-      </c>
-      <c r="D2" t="s">
-        <v>245</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1383,16 +1384,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
-      </c>
-      <c r="D3" t="s">
-        <v>245</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1400,16 +1401,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" t="s">
         <v>243</v>
-      </c>
-      <c r="D4" t="s">
-        <v>245</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1417,16 +1418,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" t="s">
         <v>243</v>
-      </c>
-      <c r="D5" t="s">
-        <v>245</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1434,16 +1435,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6" t="s">
         <v>243</v>
-      </c>
-      <c r="D6" t="s">
-        <v>245</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1451,16 +1452,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" t="s">
         <v>243</v>
-      </c>
-      <c r="D7" t="s">
-        <v>245</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1468,16 +1469,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" t="s">
         <v>243</v>
-      </c>
-      <c r="D8" t="s">
-        <v>245</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -1485,16 +1486,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1502,16 +1503,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1519,16 +1520,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1536,16 +1537,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1553,16 +1554,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1570,16 +1571,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1587,16 +1588,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" t="s">
         <v>243</v>
-      </c>
-      <c r="D15" t="s">
-        <v>245</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1604,16 +1605,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" t="s">
         <v>243</v>
-      </c>
-      <c r="D16" t="s">
-        <v>245</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1621,16 +1622,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" t="s">
         <v>243</v>
-      </c>
-      <c r="D17" t="s">
-        <v>245</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1638,16 +1639,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C18" t="s">
+        <v>241</v>
+      </c>
+      <c r="D18" t="s">
         <v>243</v>
-      </c>
-      <c r="D18" t="s">
-        <v>245</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1655,16 +1656,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" t="s">
         <v>243</v>
-      </c>
-      <c r="D19" t="s">
-        <v>245</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1672,16 +1673,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" t="s">
         <v>243</v>
-      </c>
-      <c r="D20" t="s">
-        <v>245</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1689,16 +1690,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" t="s">
         <v>243</v>
-      </c>
-      <c r="D21" t="s">
-        <v>245</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1706,16 +1707,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" t="s">
         <v>243</v>
-      </c>
-      <c r="D22" t="s">
-        <v>245</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -1723,16 +1724,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
         <v>243</v>
-      </c>
-      <c r="D23" t="s">
-        <v>245</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -1740,16 +1741,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" t="s">
         <v>243</v>
-      </c>
-      <c r="D24" t="s">
-        <v>245</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -1757,16 +1758,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
+        <v>241</v>
+      </c>
+      <c r="D25" t="s">
         <v>243</v>
-      </c>
-      <c r="D25" t="s">
-        <v>245</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1774,16 +1775,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -1791,16 +1792,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C27" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -1808,16 +1809,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C28" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -1825,16 +1826,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1842,16 +1843,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -1859,16 +1860,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -1876,16 +1877,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C32" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" t="s">
         <v>243</v>
-      </c>
-      <c r="D32" t="s">
-        <v>245</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -1893,16 +1894,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" t="s">
         <v>243</v>
-      </c>
-      <c r="D33" t="s">
-        <v>245</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -1910,16 +1911,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C34" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" t="s">
         <v>243</v>
-      </c>
-      <c r="D34" t="s">
-        <v>245</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -1927,16 +1928,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D35" t="s">
         <v>243</v>
-      </c>
-      <c r="D35" t="s">
-        <v>245</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1944,16 +1945,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" t="s">
         <v>243</v>
-      </c>
-      <c r="D36" t="s">
-        <v>245</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -1961,16 +1962,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C37" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37" t="s">
         <v>243</v>
-      </c>
-      <c r="D37" t="s">
-        <v>245</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -1978,16 +1979,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C38" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" t="s">
         <v>243</v>
-      </c>
-      <c r="D38" t="s">
-        <v>245</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -1995,16 +1996,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C39" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -2012,16 +2013,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D40" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2029,16 +2030,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D41" t="s">
         <v>243</v>
-      </c>
-      <c r="D41" t="s">
-        <v>245</v>
       </c>
       <c r="E41">
         <v>2</v>
@@ -2046,16 +2047,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C42" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" t="s">
         <v>243</v>
-      </c>
-      <c r="D42" t="s">
-        <v>245</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2063,16 +2064,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C43" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" t="s">
         <v>243</v>
-      </c>
-      <c r="D43" t="s">
-        <v>245</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -2080,16 +2081,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C44" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44" t="s">
         <v>243</v>
-      </c>
-      <c r="D44" t="s">
-        <v>245</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -2097,16 +2098,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C45" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" t="s">
         <v>243</v>
-      </c>
-      <c r="D45" t="s">
-        <v>245</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -2114,16 +2115,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C46" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" t="s">
         <v>243</v>
-      </c>
-      <c r="D46" t="s">
-        <v>245</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -2131,16 +2132,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -2148,16 +2149,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -2165,16 +2166,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C49" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -2182,16 +2183,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C50" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -2199,16 +2200,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C51" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" t="s">
         <v>243</v>
-      </c>
-      <c r="D51" t="s">
-        <v>245</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -2216,16 +2217,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C52" t="s">
+        <v>241</v>
+      </c>
+      <c r="D52" t="s">
         <v>243</v>
-      </c>
-      <c r="D52" t="s">
-        <v>245</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -2233,16 +2234,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C53" t="s">
+        <v>241</v>
+      </c>
+      <c r="D53" t="s">
         <v>243</v>
-      </c>
-      <c r="D53" t="s">
-        <v>245</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -2250,16 +2251,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C54" t="s">
+        <v>241</v>
+      </c>
+      <c r="D54" t="s">
         <v>243</v>
-      </c>
-      <c r="D54" t="s">
-        <v>245</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -2267,16 +2268,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C55" t="s">
+        <v>241</v>
+      </c>
+      <c r="D55" t="s">
         <v>243</v>
-      </c>
-      <c r="D55" t="s">
-        <v>245</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -2284,16 +2285,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D56" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -2301,16 +2302,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D57" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -2318,16 +2319,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B58" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C58" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D58" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2335,16 +2336,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -2355,13 +2356,13 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C60" t="s">
+        <v>241</v>
+      </c>
+      <c r="D60" t="s">
         <v>243</v>
-      </c>
-      <c r="D60" t="s">
-        <v>245</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -2372,13 +2373,13 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D61" t="s">
         <v>243</v>
-      </c>
-      <c r="D61" t="s">
-        <v>245</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -2389,13 +2390,13 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C62" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" t="s">
         <v>243</v>
-      </c>
-      <c r="D62" t="s">
-        <v>245</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -2406,13 +2407,13 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
+        <v>241</v>
+      </c>
+      <c r="D63" t="s">
         <v>243</v>
-      </c>
-      <c r="D63" t="s">
-        <v>245</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -2423,13 +2424,13 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C64" t="s">
+        <v>241</v>
+      </c>
+      <c r="D64" t="s">
         <v>243</v>
-      </c>
-      <c r="D64" t="s">
-        <v>245</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -2440,13 +2441,13 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C65" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65" t="s">
         <v>243</v>
-      </c>
-      <c r="D65" t="s">
-        <v>245</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -2457,13 +2458,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C66" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" t="s">
         <v>243</v>
-      </c>
-      <c r="D66" t="s">
-        <v>245</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -2474,13 +2475,13 @@
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D67" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -2491,13 +2492,13 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C68" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D68" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -2508,13 +2509,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C69" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -2525,13 +2526,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C70" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -2539,16 +2540,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B71" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C71" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" t="s">
         <v>243</v>
-      </c>
-      <c r="D71" t="s">
-        <v>245</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -2556,16 +2557,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C72" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" t="s">
         <v>243</v>
-      </c>
-      <c r="D72" t="s">
-        <v>245</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -2573,16 +2574,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B73" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C73" t="s">
+        <v>241</v>
+      </c>
+      <c r="D73" t="s">
         <v>243</v>
-      </c>
-      <c r="D73" t="s">
-        <v>245</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -2590,16 +2591,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B74" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
+        <v>241</v>
+      </c>
+      <c r="D74" t="s">
         <v>243</v>
-      </c>
-      <c r="D74" t="s">
-        <v>245</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -2607,16 +2608,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C75" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D75" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -2624,16 +2625,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B76" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C76" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D76" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -2641,16 +2642,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B77" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C77" t="s">
+        <v>241</v>
+      </c>
+      <c r="D77" t="s">
         <v>243</v>
-      </c>
-      <c r="D77" t="s">
-        <v>245</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -2658,16 +2659,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C78" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" t="s">
         <v>243</v>
-      </c>
-      <c r="D78" t="s">
-        <v>245</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -2675,16 +2676,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B79" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C79" t="s">
+        <v>241</v>
+      </c>
+      <c r="D79" t="s">
         <v>243</v>
-      </c>
-      <c r="D79" t="s">
-        <v>245</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -2692,16 +2693,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C80" t="s">
+        <v>241</v>
+      </c>
+      <c r="D80" t="s">
         <v>243</v>
-      </c>
-      <c r="D80" t="s">
-        <v>245</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -2709,16 +2710,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D81" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -2726,16 +2727,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C82" t="s">
+        <v>241</v>
+      </c>
+      <c r="D82" t="s">
         <v>243</v>
-      </c>
-      <c r="D82" t="s">
-        <v>245</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -2743,16 +2744,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
+        <v>241</v>
+      </c>
+      <c r="D83" t="s">
         <v>243</v>
-      </c>
-      <c r="D83" t="s">
-        <v>245</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -2760,16 +2761,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B84" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C84" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D84" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -2812,13 +2813,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2829,13 +2830,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2846,13 +2847,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2863,13 +2864,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2880,13 +2881,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2897,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -2914,13 +2915,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -2931,13 +2932,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -2948,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2965,13 +2966,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -2982,13 +2983,13 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2999,13 +3000,13 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3016,13 +3017,13 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -3033,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -3050,13 +3051,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -3067,13 +3068,13 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -3084,13 +3085,13 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -3101,13 +3102,13 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -3118,13 +3119,13 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -3135,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -3152,13 +3153,13 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -3169,13 +3170,13 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" t="s">
         <v>189</v>
-      </c>
-      <c r="D23" t="s">
-        <v>191</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -3186,13 +3187,13 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" t="s">
         <v>189</v>
-      </c>
-      <c r="D24" t="s">
-        <v>191</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -3203,13 +3204,13 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
         <v>189</v>
-      </c>
-      <c r="D25" t="s">
-        <v>191</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -3220,13 +3221,13 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" t="s">
         <v>189</v>
-      </c>
-      <c r="D26" t="s">
-        <v>191</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -3237,13 +3238,13 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" t="s">
         <v>189</v>
-      </c>
-      <c r="D27" t="s">
-        <v>191</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -3254,13 +3255,13 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" t="s">
         <v>189</v>
-      </c>
-      <c r="D28" t="s">
-        <v>191</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -3271,13 +3272,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" t="s">
         <v>189</v>
-      </c>
-      <c r="D29" t="s">
-        <v>191</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -3288,13 +3289,13 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
         <v>189</v>
-      </c>
-      <c r="D30" t="s">
-        <v>191</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -3305,13 +3306,13 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" t="s">
         <v>189</v>
-      </c>
-      <c r="D31" t="s">
-        <v>191</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3319,16 +3320,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
+        <v>307</v>
+      </c>
+      <c r="B32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" t="s">
         <v>188</v>
-      </c>
-      <c r="B32" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" t="s">
-        <v>190</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -3336,16 +3337,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
+        <v>307</v>
+      </c>
+      <c r="B33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
         <v>188</v>
-      </c>
-      <c r="B33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C33" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" t="s">
-        <v>190</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -3353,16 +3354,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
         <v>189</v>
-      </c>
-      <c r="D34" t="s">
-        <v>191</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -3370,16 +3371,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" t="s">
         <v>189</v>
-      </c>
-      <c r="D35" t="s">
-        <v>191</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3387,16 +3388,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
         <v>189</v>
-      </c>
-      <c r="D36" t="s">
-        <v>191</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -3404,16 +3405,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
         <v>189</v>
-      </c>
-      <c r="D37" t="s">
-        <v>191</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3421,16 +3422,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" t="s">
         <v>189</v>
-      </c>
-      <c r="D38" t="s">
-        <v>191</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -3438,16 +3439,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
         <v>189</v>
-      </c>
-      <c r="D39" t="s">
-        <v>191</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -3455,16 +3456,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
         <v>189</v>
-      </c>
-      <c r="D40" t="s">
-        <v>191</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -3472,16 +3473,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C41" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" t="s">
         <v>189</v>
-      </c>
-      <c r="D41" t="s">
-        <v>191</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -3489,16 +3490,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -3506,16 +3507,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" t="s">
         <v>189</v>
-      </c>
-      <c r="D43" t="s">
-        <v>191</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -3523,16 +3524,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C44" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" t="s">
         <v>189</v>
-      </c>
-      <c r="D44" t="s">
-        <v>191</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3540,16 +3541,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -3557,16 +3558,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D46" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3574,16 +3575,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E47">
         <v>2</v>
@@ -3591,16 +3592,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C48" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E48">
         <v>2</v>
@@ -3608,16 +3609,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" t="s">
         <v>189</v>
-      </c>
-      <c r="D49" t="s">
-        <v>191</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -3625,16 +3626,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" t="s">
         <v>189</v>
-      </c>
-      <c r="D50" t="s">
-        <v>191</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -3642,16 +3643,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s">
+        <v>187</v>
+      </c>
+      <c r="D51" t="s">
         <v>189</v>
-      </c>
-      <c r="D51" t="s">
-        <v>191</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -3659,16 +3660,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D52" t="s">
         <v>189</v>
-      </c>
-      <c r="D52" t="s">
-        <v>191</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3676,16 +3677,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" t="s">
+        <v>187</v>
+      </c>
+      <c r="D53" t="s">
         <v>189</v>
-      </c>
-      <c r="D53" t="s">
-        <v>191</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -3693,16 +3694,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C54" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D54" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -3710,16 +3711,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C55" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D55" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -3727,16 +3728,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -3744,16 +3745,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C57" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" t="s">
         <v>189</v>
-      </c>
-      <c r="D57" t="s">
-        <v>191</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -3761,16 +3762,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B58" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" t="s">
         <v>189</v>
-      </c>
-      <c r="D58" t="s">
-        <v>191</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -3778,16 +3779,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B59" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C59" t="s">
+        <v>187</v>
+      </c>
+      <c r="D59" t="s">
         <v>189</v>
-      </c>
-      <c r="D59" t="s">
-        <v>191</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -3795,16 +3796,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B60" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C60" t="s">
+        <v>187</v>
+      </c>
+      <c r="D60" t="s">
         <v>189</v>
-      </c>
-      <c r="D60" t="s">
-        <v>191</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -3812,16 +3813,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C61" t="s">
+        <v>187</v>
+      </c>
+      <c r="D61" t="s">
         <v>189</v>
-      </c>
-      <c r="D61" t="s">
-        <v>191</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -3829,16 +3830,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B62" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" t="s">
         <v>189</v>
-      </c>
-      <c r="D62" t="s">
-        <v>191</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -3849,13 +3850,13 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C63" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -3866,13 +3867,13 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C64" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -3883,13 +3884,13 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -3900,13 +3901,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C66" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -3917,13 +3918,13 @@
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E67">
         <v>2</v>
@@ -3934,13 +3935,13 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C68" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D68" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -3951,13 +3952,13 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E69">
         <v>2</v>
@@ -3968,13 +3969,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C70" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" t="s">
         <v>189</v>
-      </c>
-      <c r="D70" t="s">
-        <v>191</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -3985,13 +3986,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" t="s">
         <v>189</v>
-      </c>
-      <c r="D71" t="s">
-        <v>191</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -4002,13 +4003,13 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C72" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" t="s">
         <v>189</v>
-      </c>
-      <c r="D72" t="s">
-        <v>191</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -4019,13 +4020,13 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D73" t="s">
         <v>189</v>
-      </c>
-      <c r="D73" t="s">
-        <v>191</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -4036,13 +4037,13 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C74" t="s">
+        <v>187</v>
+      </c>
+      <c r="D74" t="s">
         <v>189</v>
-      </c>
-      <c r="D74" t="s">
-        <v>191</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -4053,13 +4054,13 @@
         <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C75" t="s">
+        <v>187</v>
+      </c>
+      <c r="D75" t="s">
         <v>189</v>
-      </c>
-      <c r="D75" t="s">
-        <v>191</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -4067,16 +4068,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B76" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D76" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4084,16 +4085,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B77" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C77" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D77" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -4101,16 +4102,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B78" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C78" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" t="s">
         <v>189</v>
-      </c>
-      <c r="D78" t="s">
-        <v>191</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -4118,16 +4119,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C79" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" t="s">
         <v>189</v>
-      </c>
-      <c r="D79" t="s">
-        <v>191</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -4135,16 +4136,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C80" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" t="s">
         <v>189</v>
-      </c>
-      <c r="D80" t="s">
-        <v>191</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -4152,16 +4153,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C81" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" t="s">
         <v>189</v>
-      </c>
-      <c r="D81" t="s">
-        <v>191</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -4169,16 +4170,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B82" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C82" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" t="s">
         <v>189</v>
-      </c>
-      <c r="D82" t="s">
-        <v>191</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -4186,16 +4187,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B83" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C83" t="s">
+        <v>187</v>
+      </c>
+      <c r="D83" t="s">
         <v>189</v>
-      </c>
-      <c r="D83" t="s">
-        <v>191</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -4203,16 +4204,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C84" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" t="s">
         <v>189</v>
-      </c>
-      <c r="D84" t="s">
-        <v>191</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -4220,16 +4221,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C85" t="s">
+        <v>187</v>
+      </c>
+      <c r="D85" t="s">
         <v>189</v>
-      </c>
-      <c r="D85" t="s">
-        <v>191</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -4237,16 +4238,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
+        <v>187</v>
+      </c>
+      <c r="D86" t="s">
         <v>189</v>
-      </c>
-      <c r="D86" t="s">
-        <v>191</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -4254,16 +4255,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C87" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" t="s">
         <v>189</v>
-      </c>
-      <c r="D87" t="s">
-        <v>191</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -4271,16 +4272,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C88" t="s">
+        <v>187</v>
+      </c>
+      <c r="D88" t="s">
         <v>189</v>
-      </c>
-      <c r="D88" t="s">
-        <v>191</v>
       </c>
       <c r="E88">
         <v>3</v>
@@ -4288,16 +4289,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="B89" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" t="s">
         <v>189</v>
-      </c>
-      <c r="D89" t="s">
-        <v>191</v>
       </c>
       <c r="E89">
         <v>3</v>
